--- a/tame_output/ON/bt/strategyON_20231213.xlsx
+++ b/tame_output/ON/bt/strategyON_20231213.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.7%</t>
+          <t>451.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-89.1%</t>
+          <t>-88.8%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.1%</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-32.4%</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.05975199725568</v>
+        <v>3.059751997255681</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227613</v>
+        <v>3.093259956227614</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.06824651857159</v>
+        <v>3.068246518571591</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408316</v>
+        <v>3.069025022408317</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708494</v>
+        <v>3.085392865708495</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968024</v>
+        <v>3.073923642968025</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066012</v>
+        <v>3.074518669066013</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293021</v>
+        <v>3.087505451293022</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239774</v>
+        <v>3.125945945239775</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167861</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216942</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454038</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780867</v>
+        <v>3.120443325780868</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.09520660653793</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597766</v>
+        <v>3.147410092597767</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527685</v>
+        <v>3.120684616527686</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844644</v>
+        <v>3.118866618844645</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502547</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.14673011872803</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702054</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487809</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.14626574482338</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524821</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068701</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714844</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083876</v>
+        <v>3.136752015083877</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666733</v>
+        <v>3.162269743666734</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097098</v>
+        <v>3.163432091097099</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762258</v>
+        <v>3.169279212762259</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583694</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742724</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589524</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872957</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946329</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43048,7 +43048,7 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.318449829143339</v>
+        <v>3.31844982914334</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308503</v>
+        <v>3.311781349308504</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257516</v>
+        <v>3.271427670257517</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.25296238744154</v>
+        <v>3.252962387441541</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43146,16 +43146,16 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>0.5333667245809354</v>
+        <v>0.5356894428272687</v>
       </c>
       <c r="E1810" t="n">
-        <v>3.332060596295415</v>
+        <v>3.332989683593948</v>
       </c>
       <c r="F1810" t="n">
-        <v>1.76668176609239</v>
+        <v>1.769004484338723</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.179079390432222</v>
+        <v>4.180473021380022</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231213.xlsx
+++ b/tame_output/ON/bt/strategyON_20231213.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-88.8%</t>
+          <t>-88.7%</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.2%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.5%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
     </row>
@@ -42059,7 +42059,7 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050895742336375</v>
+        <v>3.050895742336374</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
@@ -42082,7 +42082,7 @@
         <v>45226</v>
       </c>
       <c r="B1764" t="n">
-        <v>3.049222094320088</v>
+        <v>3.049222094320087</v>
       </c>
       <c r="C1764" t="n">
         <v>3.030639375029551</v>
@@ -42128,7 +42128,7 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055423383477762</v>
+        <v>3.055423383477761</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255681</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227614</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.068246518571591</v>
+        <v>3.06824651857159</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408317</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708495</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968025</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -43146,16 +43146,16 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>0.5356894428272687</v>
+        <v>0.5368633845718054</v>
       </c>
       <c r="E1810" t="n">
-        <v>3.332989683593948</v>
+        <v>3.333459260291762</v>
       </c>
       <c r="F1810" t="n">
-        <v>1.769004484338723</v>
+        <v>1.77017842608326</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.180473021380022</v>
+        <v>4.181177386426745</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231213.xlsx
+++ b/tame_output/ON/bt/strategyON_20231213.xlsx
@@ -595,12 +595,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -934,17 +934,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -954,15 +954,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-11-05</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-383.0%</t>
+          <t>-401.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.6%</t>
+          <t>426.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-168.2%</t>
+          <t>-166.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-88.7%</t>
+          <t>-105.4%</t>
         </is>
       </c>
     </row>
@@ -1054,22 +1054,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,15 +1107,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-141.7%</t>
+          <t>-149.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-15.8%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1260,15 +1260,15 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-166.7%</t>
+          <t>-184.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.5%</t>
+          <t>-141.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-48.9%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1413,15 +1413,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-88.5%</t>
+          <t>-99.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,22 +1451,22 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>106.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
     </row>
@@ -42059,7 +42059,7 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050895742336374</v>
+        <v>3.050895742336375</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
@@ -42088,16 +42088,16 @@
         <v>3.030639375029551</v>
       </c>
       <c r="D1764" t="n">
-        <v>-2.264784380974227</v>
+        <v>-2.44678639185837</v>
       </c>
       <c r="E1764" t="n">
-        <v>2.124369198326114</v>
+        <v>2.051568393972456</v>
       </c>
       <c r="F1764" t="n">
-        <v>0.5079233531459244</v>
+        <v>0.3259213422617812</v>
       </c>
       <c r="G1764" t="n">
-        <v>3.335393386917108</v>
+        <v>3.226192180386622</v>
       </c>
     </row>
     <row r="1765">
@@ -42111,16 +42111,16 @@
         <v>3.030564355893199</v>
       </c>
       <c r="D1765" t="n">
-        <v>-2.261046424913171</v>
+        <v>-2.443048435797314</v>
       </c>
       <c r="E1765" t="n">
-        <v>2.125789361614183</v>
+        <v>2.052988557260526</v>
       </c>
       <c r="F1765" t="n">
-        <v>0.5102998054265492</v>
+        <v>0.328297794542406</v>
       </c>
       <c r="G1765" t="n">
-        <v>3.33674423914913</v>
+        <v>3.227543032618644</v>
       </c>
     </row>
     <row r="1766">
@@ -42134,16 +42134,16 @@
         <v>3.028879780391293</v>
       </c>
       <c r="D1766" t="n">
-        <v>-2.252549279252038</v>
+        <v>-2.434551290136181</v>
       </c>
       <c r="E1766" t="n">
-        <v>2.127503644376731</v>
+        <v>2.054702840023074</v>
       </c>
       <c r="F1766" t="n">
-        <v>0.5102998054265492</v>
+        <v>0.328297794542406</v>
       </c>
       <c r="G1766" t="n">
-        <v>3.335059663647224</v>
+        <v>3.225858457116738</v>
       </c>
     </row>
     <row r="1767">
@@ -42157,16 +42157,16 @@
         <v>3.033268356072139</v>
       </c>
       <c r="D1767" t="n">
-        <v>-2.252241319167314</v>
+        <v>-2.434243330051457</v>
       </c>
       <c r="E1767" t="n">
-        <v>2.132015404091467</v>
+        <v>2.05921459973781</v>
       </c>
       <c r="F1767" t="n">
-        <v>0.5114815195192493</v>
+        <v>0.3294795086351061</v>
       </c>
       <c r="G1767" t="n">
-        <v>3.34015726778369</v>
+        <v>3.230956061253204</v>
       </c>
     </row>
     <row r="1768">
@@ -42180,16 +42180,16 @@
         <v>3.034928653249013</v>
       </c>
       <c r="D1768" t="n">
-        <v>-2.250459556796722</v>
+        <v>-2.432461567680865</v>
       </c>
       <c r="E1768" t="n">
-        <v>2.134388406216578</v>
+        <v>2.06158760186292</v>
       </c>
       <c r="F1768" t="n">
-        <v>0.5114815195192493</v>
+        <v>0.3294795086351061</v>
       </c>
       <c r="G1768" t="n">
-        <v>3.341817564960565</v>
+        <v>3.232616358430079</v>
       </c>
     </row>
     <row r="1769">
@@ -42203,16 +42203,16 @@
         <v>3.049962823512704</v>
       </c>
       <c r="D1769" t="n">
-        <v>-2.254536911933814</v>
+        <v>-2.436538922817957</v>
       </c>
       <c r="E1769" t="n">
-        <v>2.147791634425432</v>
+        <v>2.074990830071774</v>
       </c>
       <c r="F1769" t="n">
-        <v>0.5114815195192493</v>
+        <v>0.3294795086351061</v>
       </c>
       <c r="G1769" t="n">
-        <v>3.356851735224255</v>
+        <v>3.247650528693769</v>
       </c>
     </row>
     <row r="1770">
@@ -42226,16 +42226,16 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-2.244544831007405</v>
+        <v>-2.426546841891548</v>
       </c>
       <c r="E1770" t="n">
-        <v>2.150102901460128</v>
+        <v>2.077302097106471</v>
       </c>
       <c r="F1770" t="n">
-        <v>0.5214736004456584</v>
+        <v>0.3394715895615152</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.361161418444234</v>
+        <v>3.251960211913748</v>
       </c>
     </row>
     <row r="1771">
@@ -42249,16 +42249,16 @@
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-2.245100586063443</v>
+        <v>-2.427102596947586</v>
       </c>
       <c r="E1771" t="n">
-        <v>2.152782409334304</v>
+        <v>2.079981604980647</v>
       </c>
       <c r="F1771" t="n">
-        <v>0.5198661866845804</v>
+        <v>0.3378641758004373</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.363098780084178</v>
+        <v>3.253897573553692</v>
       </c>
     </row>
     <row r="1772">
@@ -42272,16 +42272,16 @@
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-2.248314938476754</v>
+        <v>-2.430316949360897</v>
       </c>
       <c r="E1772" t="n">
-        <v>2.157021657508127</v>
+        <v>2.084220853154469</v>
       </c>
       <c r="F1772" t="n">
-        <v>0.5198661866845804</v>
+        <v>0.3378641758004373</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.368623769223325</v>
+        <v>3.259422562692839</v>
       </c>
     </row>
     <row r="1773">
@@ -42295,16 +42295,16 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-2.265323183879363</v>
+        <v>-2.447325194763506</v>
       </c>
       <c r="E1773" t="n">
-        <v>2.151295931984814</v>
+        <v>2.078495127631157</v>
       </c>
       <c r="F1773" t="n">
-        <v>0.5228653216975542</v>
+        <v>0.340863310813411</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.371500822868841</v>
+        <v>3.262299616338355</v>
       </c>
     </row>
     <row r="1774">
@@ -42318,16 +42318,16 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-2.246363461428009</v>
+        <v>-2.428365472312152</v>
       </c>
       <c r="E1774" t="n">
-        <v>2.159629683136629</v>
+        <v>2.086828878782972</v>
       </c>
       <c r="F1774" t="n">
-        <v>0.5228653216975542</v>
+        <v>0.340863310813411</v>
       </c>
       <c r="G1774" t="n">
-        <v>3.372250685040114</v>
+        <v>3.263049478509628</v>
       </c>
     </row>
     <row r="1775">
@@ -42341,16 +42341,16 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-2.2451287368252</v>
+        <v>-2.427130747709343</v>
       </c>
       <c r="E1775" t="n">
-        <v>2.158359170441333</v>
+        <v>2.085558366087676</v>
       </c>
       <c r="F1775" t="n">
-        <v>0.5228653216975542</v>
+        <v>0.340863310813411</v>
       </c>
       <c r="G1775" t="n">
-        <v>3.370486282503695</v>
+        <v>3.261285075973209</v>
       </c>
     </row>
     <row r="1776">
@@ -42364,16 +42364,16 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-2.255163000648849</v>
+        <v>-2.437165011532992</v>
       </c>
       <c r="E1776" t="n">
-        <v>2.157913074748736</v>
+        <v>2.085112270395078</v>
       </c>
       <c r="F1776" t="n">
-        <v>0.5228653216975542</v>
+        <v>0.340863310813411</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.374053892340557</v>
+        <v>3.26485268581007</v>
       </c>
     </row>
     <row r="1777">
@@ -42387,16 +42387,16 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-2.260201998946716</v>
+        <v>-2.442204009830859</v>
       </c>
       <c r="E1777" t="n">
-        <v>2.179879437319198</v>
+        <v>2.10707863296554</v>
       </c>
       <c r="F1777" t="n">
-        <v>0.5178263233996874</v>
+        <v>0.3358243125155443</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.395012455251445</v>
+        <v>3.285811248720959</v>
       </c>
     </row>
     <row r="1778">
@@ -42410,16 +42410,16 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-2.250382280786165</v>
+        <v>-2.432384291670308</v>
       </c>
       <c r="E1778" t="n">
-        <v>2.181276036070648</v>
+        <v>2.10847523171699</v>
       </c>
       <c r="F1778" t="n">
-        <v>0.5242562636163748</v>
+        <v>0.3422542527322317</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.396339130868687</v>
+        <v>3.287137924338202</v>
       </c>
     </row>
     <row r="1779">
@@ -42433,16 +42433,16 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-2.248580653947211</v>
+        <v>-2.430582664831354</v>
       </c>
       <c r="E1779" t="n">
-        <v>2.167245248809855</v>
+        <v>2.094444444456198</v>
       </c>
       <c r="F1779" t="n">
-        <v>0.5242562636163748</v>
+        <v>0.3422542527322317</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.381587692872313</v>
+        <v>3.272386486341827</v>
       </c>
     </row>
     <row r="1780">
@@ -42456,16 +42456,16 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-2.247591972203043</v>
+        <v>-2.429593983087186</v>
       </c>
       <c r="E1780" t="n">
-        <v>2.165754477823195</v>
+        <v>2.092953673469538</v>
       </c>
       <c r="F1780" t="n">
-        <v>0.5242562636163748</v>
+        <v>0.3422542527322317</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.379701449187985</v>
+        <v>3.2705002426575</v>
       </c>
     </row>
     <row r="1781">
@@ -42479,16 +42479,16 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-2.239595617681505</v>
+        <v>-2.421597628565648</v>
       </c>
       <c r="E1781" t="n">
-        <v>2.17092664608765</v>
+        <v>2.098125841733993</v>
       </c>
       <c r="F1781" t="n">
-        <v>0.5322526181379134</v>
+        <v>0.3502506072537703</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.386472888356749</v>
+        <v>3.277271681826263</v>
       </c>
     </row>
     <row r="1782">
@@ -42502,16 +42502,16 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-2.234611867009596</v>
+        <v>-2.416613877893739</v>
       </c>
       <c r="E1782" t="n">
-        <v>2.184758726947325</v>
+        <v>2.111957922593668</v>
       </c>
       <c r="F1782" t="n">
-        <v>0.5372363688098221</v>
+        <v>0.355234357925679</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.401301719350806</v>
+        <v>3.29210051282032</v>
       </c>
     </row>
     <row r="1783">
@@ -42525,16 +42525,16 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-2.22822572806004</v>
+        <v>-2.410227738944184</v>
       </c>
       <c r="E1783" t="n">
-        <v>2.194041385538937</v>
+        <v>2.121240581185279</v>
       </c>
       <c r="F1783" t="n">
-        <v>0.5372363688098221</v>
+        <v>0.355234357925679</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.408029922362595</v>
+        <v>3.298828715832109</v>
       </c>
     </row>
     <row r="1784">
@@ -42548,16 +42548,16 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-2.240031078378673</v>
+        <v>-2.422033089262816</v>
       </c>
       <c r="E1784" t="n">
-        <v>2.193335334171026</v>
+        <v>2.120534529817369</v>
       </c>
       <c r="F1784" t="n">
-        <v>0.5254310184911894</v>
+        <v>0.3434290076070464</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.404962800930957</v>
+        <v>3.295761594400472</v>
       </c>
     </row>
     <row r="1785">
@@ -42571,16 +42571,16 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-2.231299267600007</v>
+        <v>-2.41330127848415</v>
       </c>
       <c r="E1785" t="n">
-        <v>2.202775516092382</v>
+        <v>2.129974711738725</v>
       </c>
       <c r="F1785" t="n">
-        <v>0.5341628292698557</v>
+        <v>0.3521608183857126</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.416149345008046</v>
+        <v>3.306948138477561</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-2.224962380955555</v>
+        <v>-2.406964391839698</v>
       </c>
       <c r="E1786" t="n">
-        <v>2.200621089698148</v>
+        <v>2.127820285344491</v>
       </c>
       <c r="F1786" t="n">
-        <v>0.5341628292698557</v>
+        <v>0.3521608183857126</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.411460163956032</v>
+        <v>3.302258957425546</v>
       </c>
     </row>
     <row r="1787">
@@ -42617,16 +42617,16 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-2.222427933228186</v>
+        <v>-2.40442994411233</v>
       </c>
       <c r="E1787" t="n">
-        <v>2.211597526591289</v>
+        <v>2.138796722237632</v>
       </c>
       <c r="F1787" t="n">
-        <v>0.5341628292698557</v>
+        <v>0.3521608183857126</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.421422821758226</v>
+        <v>3.31222161522774</v>
       </c>
     </row>
     <row r="1788">
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-2.222503832208791</v>
+        <v>-2.404505843092934</v>
       </c>
       <c r="E1788" t="n">
-        <v>2.203981847191957</v>
+        <v>2.1311810428383</v>
       </c>
       <c r="F1788" t="n">
-        <v>0.5349260899591826</v>
+        <v>0.3529240790750395</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.414295458364732</v>
+        <v>3.305094251834246</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-2.233006021768138</v>
+        <v>-2.415008032652281</v>
       </c>
       <c r="E1789" t="n">
-        <v>2.177545547158592</v>
+        <v>2.104744742804935</v>
       </c>
       <c r="F1789" t="n">
-        <v>0.5244239003998359</v>
+        <v>0.3424218895156929</v>
       </c>
       <c r="G1789" t="n">
-        <v>3.385758720419497</v>
+        <v>3.276557513889011</v>
       </c>
     </row>
     <row r="1790">
@@ -42686,16 +42686,16 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-2.234839284447254</v>
+        <v>-2.416841295331397</v>
       </c>
       <c r="E1790" t="n">
-        <v>2.177513081933067</v>
+        <v>2.10471227757941</v>
       </c>
       <c r="F1790" t="n">
-        <v>0.5244239003998359</v>
+        <v>0.3424218895156929</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.386459560265619</v>
+        <v>3.277258353735133</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-2.239848399508838</v>
+        <v>-2.421850410392981</v>
       </c>
       <c r="E1791" t="n">
-        <v>2.176026515737293</v>
+        <v>2.103225711383636</v>
       </c>
       <c r="F1791" t="n">
-        <v>0.5234293228413012</v>
+        <v>0.3414273119571581</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.386379893559357</v>
+        <v>3.277178687028871</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-2.243553956145652</v>
+        <v>-2.425555967029795</v>
       </c>
       <c r="E1792" t="n">
-        <v>2.173772018322933</v>
+        <v>2.100971213969275</v>
       </c>
       <c r="F1792" t="n">
-        <v>0.5215596475836662</v>
+        <v>0.3395576366995232</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.384485813645142</v>
+        <v>3.275284607114656</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-2.242321630788287</v>
+        <v>-2.42432364167243</v>
       </c>
       <c r="E1793" t="n">
-        <v>2.174684800528198</v>
+        <v>2.101883996174541</v>
       </c>
       <c r="F1793" t="n">
-        <v>0.5221900239557038</v>
+        <v>0.3401880130715608</v>
       </c>
       <c r="G1793" t="n">
-        <v>3.385283891530683</v>
+        <v>3.276082685000198</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-2.231993633772435</v>
+        <v>-2.413995644656578</v>
       </c>
       <c r="E1794" t="n">
-        <v>2.182945907498752</v>
+        <v>2.110145103145095</v>
       </c>
       <c r="F1794" t="n">
-        <v>0.532518020971556</v>
+        <v>0.350516010087413</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.395610597904408</v>
+        <v>3.286409391373923</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-2.231877298624879</v>
+        <v>-2.413879309509022</v>
       </c>
       <c r="E1795" t="n">
-        <v>2.189513101759611</v>
+        <v>2.116712297405954</v>
       </c>
       <c r="F1795" t="n">
-        <v>0.5326343561191117</v>
+        <v>0.3506323452349687</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.402201059194778</v>
+        <v>3.292999852664292</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-2.233722708201746</v>
+        <v>-2.415724719085889</v>
       </c>
       <c r="E1796" t="n">
-        <v>2.185748908374253</v>
+        <v>2.112948104020596</v>
       </c>
       <c r="F1796" t="n">
-        <v>0.5326343561191117</v>
+        <v>0.3506323452349687</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.399175029640166</v>
+        <v>3.289973823109681</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-2.232224275676647</v>
+        <v>-2.41422628656079</v>
       </c>
       <c r="E1797" t="n">
-        <v>2.186286569245425</v>
+        <v>2.113485764891768</v>
       </c>
       <c r="F1797" t="n">
-        <v>0.5341327886442107</v>
+        <v>0.3521307777600676</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.400012377016359</v>
+        <v>3.290811170485874</v>
       </c>
     </row>
     <row r="1798">
@@ -42870,16 +42870,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-2.240288527869381</v>
+        <v>-2.422290538753524</v>
       </c>
       <c r="E1798" t="n">
-        <v>2.184338846311644</v>
+        <v>2.111538041957986</v>
       </c>
       <c r="F1798" t="n">
-        <v>0.5260685364514768</v>
+        <v>0.3440665255673337</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.396451803644031</v>
+        <v>3.287250597113545</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-2.241618495330593</v>
+        <v>-2.423620506214736</v>
       </c>
       <c r="E1799" t="n">
-        <v>2.183806859327159</v>
+        <v>2.111006054973501</v>
       </c>
       <c r="F1799" t="n">
-        <v>0.5260685364514768</v>
+        <v>0.3440665255673337</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.396451803644031</v>
+        <v>3.287250597113545</v>
       </c>
     </row>
     <row r="1800">
@@ -42916,16 +42916,16 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-2.013753812597082</v>
+        <v>-2.195755823481226</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.277169205527725</v>
+        <v>2.204368401174068</v>
       </c>
       <c r="F1800" t="n">
-        <v>0.5260685364514768</v>
+        <v>0.3440665255673337</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.398668276751193</v>
+        <v>3.289467070220707</v>
       </c>
     </row>
     <row r="1801">
@@ -42939,16 +42939,16 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-1.765652248729866</v>
+        <v>-1.947654259614009</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.383944427419704</v>
+        <v>2.311143623066047</v>
       </c>
       <c r="F1801" t="n">
-        <v>0.5260685364514768</v>
+        <v>0.3440665255673337</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.406202873096285</v>
+        <v>3.297001666565799</v>
       </c>
     </row>
     <row r="1802">
@@ -42962,16 +42962,16 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-1.468813849336535</v>
+        <v>-1.650815860220678</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.504102798150494</v>
+        <v>2.431301993796837</v>
       </c>
       <c r="F1802" t="n">
-        <v>0.6409230249326044</v>
+        <v>0.4589210140484614</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.476538577158419</v>
+        <v>3.367337370627933</v>
       </c>
     </row>
     <row r="1803">
@@ -42985,16 +42985,16 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-1.165174292511099</v>
+        <v>-1.347176303395242</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.627235695346355</v>
+        <v>2.554434890992697</v>
       </c>
       <c r="F1803" t="n">
-        <v>0.6409230249326044</v>
+        <v>0.4589210140484614</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.478215651624105</v>
+        <v>3.36901444509362</v>
       </c>
     </row>
     <row r="1804">
@@ -43008,16 +43008,16 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-0.8761536860703902</v>
+        <v>-1.058155696954533</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.738783359372096</v>
+        <v>2.665982555018438</v>
       </c>
       <c r="F1804" t="n">
-        <v>0.6409230249326044</v>
+        <v>0.4589210140484614</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.474155073073563</v>
+        <v>3.364953866543077</v>
       </c>
     </row>
     <row r="1805">
@@ -43031,16 +43031,16 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-0.5914337588064931</v>
+        <v>-0.7734357696906362</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.857891469621672</v>
+        <v>2.785090665268015</v>
       </c>
       <c r="F1805" t="n">
-        <v>0.9256429521965016</v>
+        <v>0.7436409413123586</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.650207168775919</v>
+        <v>3.541005962245433</v>
       </c>
     </row>
     <row r="1806">
@@ -43054,16 +43054,16 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-0.3076720893149527</v>
+        <v>-0.4896741001990959</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.976708300592096</v>
+        <v>2.903907496238438</v>
       </c>
       <c r="F1806" t="n">
-        <v>0.9256429521965016</v>
+        <v>0.7436409413123586</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.655519331949726</v>
+        <v>3.54631812541924</v>
       </c>
     </row>
     <row r="1807">
@@ -43077,16 +43077,16 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-0.04602369492231206</v>
+        <v>-0.2280257058064552</v>
       </c>
       <c r="E1807" t="n">
-        <v>3.074610245795785</v>
+        <v>3.001809441442128</v>
       </c>
       <c r="F1807" t="n">
-        <v>1.187291346589142</v>
+        <v>1.005289335704999</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.805750956031944</v>
+        <v>3.696549749501458</v>
       </c>
     </row>
     <row r="1808">
@@ -43100,16 +43100,16 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>0.2681427432170204</v>
+        <v>0.08614073233287722</v>
       </c>
       <c r="E1808" t="n">
-        <v>3.197740496067631</v>
+        <v>3.124939691713974</v>
       </c>
       <c r="F1808" t="n">
-        <v>1.501457784728475</v>
+        <v>1.319455773844332</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.991714493931656</v>
+        <v>3.88251328740117</v>
       </c>
     </row>
     <row r="1809">
@@ -43123,16 +43123,16 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>0.3906544473227928</v>
+        <v>0.2086524364386496</v>
       </c>
       <c r="E1809" t="n">
-        <v>3.265159561336679</v>
+        <v>3.192358756983022</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.623969488834247</v>
+        <v>1.441967477950104</v>
       </c>
       <c r="G1809" t="n">
-        <v>4.083635900021858</v>
+        <v>3.974434693491372</v>
       </c>
     </row>
     <row r="1810">
@@ -43140,22 +43140,22 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.078172328527073</v>
+        <v>3.071898379875592</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>0.5368633845718054</v>
+        <v>0.370040970365378</v>
       </c>
       <c r="E1810" t="n">
-        <v>3.333459260291762</v>
+        <v>3.266730294609192</v>
       </c>
       <c r="F1810" t="n">
-        <v>1.77017842608326</v>
+        <v>1.603356011876833</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.181177386426745</v>
+        <v>4.081083937902888</v>
       </c>
     </row>
   </sheetData>
